--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-12-2025.xlsx
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£35.57</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
